--- a/PKSim/Analog15_PKSim.xlsx
+++ b/PKSim/Analog15_PKSim.xlsx
@@ -6,7 +6,7 @@
     <workbookView tabRatio="600"/>
   </bookViews>
   <sheets>
-    <sheet name="Analog15_PKSim" sheetId="1" r:id="rId3"/>
+    <sheet name="Analog17_PKSim" sheetId="1" r:id="rId3"/>
     <sheet name="Global PK-Analyses" sheetId="2" r:id="rId4"/>
     <sheet name="PK-Analyses" sheetId="3" r:id="rId5"/>
   </sheets>
@@ -19,16 +19,16 @@
     <t xml:space="preserve">Time [h]</t>
   </si>
   <si>
-    <t xml:space="preserve">Analog15-Peripheral Venous Blood-Plasma-Concentration [µmol/l]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog15-Arterial Blood-Plasma-Concentration [µmol/l]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog15-Brain-Tissue-Concentration [µmol/l]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog15-Liver-Tissue-Concentration [µmol/l]</t>
+    <t xml:space="preserve">Analog17-Peripheral Venous Blood-Plasma-Concentration [µmol/l]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analog17-Arterial Blood-Plasma-Concentration [µmol/l]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analog17-Brain-Tissue-Concentration [µmol/l]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analog17-Liver-Tissue-Concentration [µmol/l]</t>
   </si>
   <si>
     <t xml:space="preserve">Parameter</t>
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Vss (plasma)</t>
   </si>
   <si>
-    <t xml:space="preserve">Analog15</t>
+    <t xml:space="preserve">Analog17</t>
   </si>
   <si>
     <t xml:space="preserve">ml/kg</t>
@@ -64,16 +64,16 @@
     <t xml:space="preserve">Vss (phys-chem)</t>
   </si>
   <si>
-    <t xml:space="preserve">Analog15 - Analog15-Arterial Blood-Plasma-Concentration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog15 - Analog15-Brain-Tissue-Concentration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog15 - Analog15-Liver-Tissue-Concentration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog15 - Analog15-Peripheral Venous Blood-Plasma-Concentration</t>
+    <t xml:space="preserve">Analog17 - Analog17-Arterial Blood-Plasma-Concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analog17 - Analog17-Brain-Tissue-Concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analog17 - Analog17-Liver-Tissue-Concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analog17 - Analog17-Peripheral Venous Blood-Plasma-Concentration</t>
   </si>
   <si>
     <t xml:space="preserve">AUC_inf [µmol*min/l]</t>
@@ -218,16 +218,16 @@
         <v>0.05</v>
       </c>
       <c r="B3" s="2">
-        <v>0.00138943</v>
+        <v>0.001367437</v>
       </c>
       <c r="C3" s="2">
-        <v>0.001053748</v>
+        <v>0.001043372</v>
       </c>
       <c r="D3" s="2">
-        <v>2.939583E-06</v>
+        <v>2.91697E-06</v>
       </c>
       <c r="E3" s="2">
-        <v>0.001671691</v>
+        <v>0.001612236</v>
       </c>
     </row>
     <row r="4">
@@ -235,16 +235,16 @@
         <v>0.1</v>
       </c>
       <c r="B4" s="2">
-        <v>0.0008757242</v>
+        <v>0.0008761148</v>
       </c>
       <c r="C4" s="2">
-        <v>0.0007182305</v>
+        <v>0.0007282975</v>
       </c>
       <c r="D4" s="2">
-        <v>2.527488E-06</v>
+        <v>2.531447E-06</v>
       </c>
       <c r="E4" s="2">
-        <v>0.00207135</v>
+        <v>0.001973585</v>
       </c>
     </row>
     <row r="5">
@@ -252,16 +252,16 @@
         <v>0.15</v>
       </c>
       <c r="B5" s="2">
-        <v>0.0006552798</v>
+        <v>0.0006664781</v>
       </c>
       <c r="C5" s="2">
-        <v>0.0006200493</v>
+        <v>0.0006343074</v>
       </c>
       <c r="D5" s="2">
-        <v>2.602896E-06</v>
+        <v>2.621199E-06</v>
       </c>
       <c r="E5" s="2">
-        <v>0.002031183</v>
+        <v>0.001907141</v>
       </c>
     </row>
     <row r="6">
@@ -269,16 +269,16 @@
         <v>0.2</v>
       </c>
       <c r="B6" s="2">
-        <v>0.0005582898</v>
+        <v>0.0005714747</v>
       </c>
       <c r="C6" s="2">
-        <v>0.0005618122</v>
+        <v>0.0005735978</v>
       </c>
       <c r="D6" s="2">
-        <v>2.73075E-06</v>
+        <v>2.75141E-06</v>
       </c>
       <c r="E6" s="2">
-        <v>0.00187006</v>
+        <v>0.001735141</v>
       </c>
     </row>
     <row r="7">
@@ -286,16 +286,16 @@
         <v>0.25</v>
       </c>
       <c r="B7" s="2">
-        <v>0.0005040811</v>
+        <v>0.0005158559</v>
       </c>
       <c r="C7" s="2">
-        <v>0.0005147753</v>
+        <v>0.0005233713</v>
       </c>
       <c r="D7" s="2">
-        <v>2.859098E-06</v>
+        <v>2.879074E-06</v>
       </c>
       <c r="E7" s="2">
-        <v>0.001691533</v>
+        <v>0.001556034</v>
       </c>
     </row>
     <row r="8">
@@ -303,16 +303,16 @@
         <v>0.3</v>
       </c>
       <c r="B8" s="2">
-        <v>0.0004655244</v>
+        <v>0.0004752754</v>
       </c>
       <c r="C8" s="2">
-        <v>0.0004742266</v>
+        <v>0.0004803359</v>
       </c>
       <c r="D8" s="2">
-        <v>2.981336E-06</v>
+        <v>3.000419E-06</v>
       </c>
       <c r="E8" s="2">
-        <v>0.001526831</v>
+        <v>0.001396139</v>
       </c>
     </row>
     <row r="9">
@@ -320,16 +320,16 @@
         <v>0.35</v>
       </c>
       <c r="B9" s="2">
-        <v>0.0004342415</v>
+        <v>0.0004422266</v>
       </c>
       <c r="C9" s="2">
-        <v>0.0004390721</v>
+        <v>0.00044347</v>
       </c>
       <c r="D9" s="2">
-        <v>3.097625E-06</v>
+        <v>3.116184E-06</v>
       </c>
       <c r="E9" s="2">
-        <v>0.001383316</v>
+        <v>0.001259808</v>
       </c>
     </row>
     <row r="10">
@@ -337,16 +337,16 @@
         <v>0.4</v>
       </c>
       <c r="B10" s="2">
-        <v>0.0004075304</v>
+        <v>0.0004142064</v>
       </c>
       <c r="C10" s="2">
-        <v>0.0004086413</v>
+        <v>0.0004119283</v>
       </c>
       <c r="D10" s="2">
-        <v>3.208811E-06</v>
+        <v>3.227252E-06</v>
       </c>
       <c r="E10" s="2">
-        <v>0.00126063</v>
+        <v>0.001145</v>
       </c>
     </row>
     <row r="11">
@@ -354,16 +354,16 @@
         <v>0.45</v>
       </c>
       <c r="B11" s="2">
-        <v>0.0003843494</v>
+        <v>0.0003900701</v>
       </c>
       <c r="C11" s="2">
-        <v>0.0003822926</v>
+        <v>0.0003848783</v>
       </c>
       <c r="D11" s="2">
-        <v>3.315587E-06</v>
+        <v>3.334216E-06</v>
       </c>
       <c r="E11" s="2">
-        <v>0.001156172</v>
+        <v>0.00104837</v>
       </c>
     </row>
     <row r="12">
@@ -371,16 +371,16 @@
         <v>0.5</v>
       </c>
       <c r="B12" s="2">
-        <v>0.000364058</v>
+        <v>0.0003691078</v>
       </c>
       <c r="C12" s="2">
-        <v>0.000359413</v>
+        <v>0.0003615708</v>
       </c>
       <c r="D12" s="2">
-        <v>3.418444E-06</v>
+        <v>3.437479E-06</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0010671</v>
+        <v>0.0009666884</v>
       </c>
     </row>
     <row r="13">
@@ -388,16 +388,16 @@
         <v>0.55</v>
       </c>
       <c r="B13" s="2">
-        <v>0.0003461868</v>
+        <v>0.0003507673</v>
       </c>
       <c r="C13" s="2">
-        <v>0.0003394602</v>
+        <v>0.0003413689</v>
       </c>
       <c r="D13" s="2">
-        <v>3.517757E-06</v>
+        <v>3.537353E-06</v>
       </c>
       <c r="E13" s="2">
-        <v>0.0009908399</v>
+        <v>0.0008972394</v>
       </c>
     </row>
     <row r="14">
@@ -405,16 +405,16 @@
         <v>0.6</v>
       </c>
       <c r="B14" s="2">
-        <v>0.0003303785</v>
+        <v>0.0003346025</v>
       </c>
       <c r="C14" s="2">
-        <v>0.0003219704</v>
+        <v>0.0003237455</v>
       </c>
       <c r="D14" s="2">
-        <v>3.61383E-06</v>
+        <v>3.634096E-06</v>
       </c>
       <c r="E14" s="2">
-        <v>0.0009251807</v>
+        <v>0.0008378131</v>
       </c>
     </row>
     <row r="15">
@@ -422,16 +422,16 @@
         <v>0.65</v>
       </c>
       <c r="B15" s="2">
-        <v>0.0003163049</v>
+        <v>0.0003202528</v>
       </c>
       <c r="C15" s="2">
-        <v>0.0003065516</v>
+        <v>0.0003082681</v>
       </c>
       <c r="D15" s="2">
-        <v>3.706912E-06</v>
+        <v>3.727929E-06</v>
       </c>
       <c r="E15" s="2">
-        <v>0.0008683322</v>
+        <v>0.0007866248</v>
       </c>
     </row>
     <row r="16">
@@ -439,16 +439,16 @@
         <v>0.7</v>
       </c>
       <c r="B16" s="2">
-        <v>0.0003036935</v>
+        <v>0.0003074243</v>
       </c>
       <c r="C16" s="2">
-        <v>0.0002928805</v>
+        <v>0.0002945844</v>
       </c>
       <c r="D16" s="2">
-        <v>3.797224E-06</v>
+        <v>3.819048E-06</v>
       </c>
       <c r="E16" s="2">
-        <v>0.0008188394</v>
+        <v>0.0007422454</v>
       </c>
     </row>
     <row r="17">
@@ -456,16 +456,16 @@
         <v>0.75</v>
       </c>
       <c r="B17" s="2">
-        <v>0.0002923277</v>
+        <v>0.0002958751</v>
       </c>
       <c r="C17" s="2">
-        <v>0.000280689</v>
+        <v>0.0002824059</v>
       </c>
       <c r="D17" s="2">
-        <v>3.884959E-06</v>
+        <v>3.907628E-06</v>
       </c>
       <c r="E17" s="2">
-        <v>0.0007754993</v>
+        <v>0.0007035194</v>
       </c>
     </row>
     <row r="18">
@@ -473,16 +473,16 @@
         <v>0.8</v>
       </c>
       <c r="B18" s="2">
-        <v>0.0002820208</v>
+        <v>0.0002854076</v>
       </c>
       <c r="C18" s="2">
-        <v>0.0002697533</v>
+        <v>0.0002714956</v>
       </c>
       <c r="D18" s="2">
-        <v>3.970287E-06</v>
+        <v>3.993825E-06</v>
       </c>
       <c r="E18" s="2">
-        <v>0.0007373323</v>
+        <v>0.0006695056</v>
       </c>
     </row>
     <row r="19">
@@ -490,16 +490,16 @@
         <v>0.85</v>
       </c>
       <c r="B19" s="2">
-        <v>0.0002726188</v>
+        <v>0.0002758593</v>
       </c>
       <c r="C19" s="2">
-        <v>0.0002598886</v>
+        <v>0.0002616577</v>
       </c>
       <c r="D19" s="2">
-        <v>4.053362E-06</v>
+        <v>4.077778E-06</v>
       </c>
       <c r="E19" s="2">
-        <v>0.0007035334</v>
+        <v>0.0006394343</v>
       </c>
     </row>
     <row r="20">
@@ -507,16 +507,16 @@
         <v>0.9</v>
       </c>
       <c r="B20" s="2">
-        <v>0.0002639945</v>
+        <v>0.0002670964</v>
       </c>
       <c r="C20" s="2">
-        <v>0.0002509405</v>
+        <v>0.0002527309</v>
       </c>
       <c r="D20" s="2">
-        <v>4.134318E-06</v>
+        <v>4.159612E-06</v>
       </c>
       <c r="E20" s="2">
-        <v>0.0006734352</v>
+        <v>0.0006126755</v>
       </c>
     </row>
     <row r="21">
@@ -524,16 +524,16 @@
         <v>0.95</v>
       </c>
       <c r="B21" s="2">
-        <v>0.0002560422</v>
+        <v>0.0002590081</v>
       </c>
       <c r="C21" s="2">
-        <v>0.0002427795</v>
+        <v>0.0002445817</v>
       </c>
       <c r="D21" s="2">
-        <v>4.213278E-06</v>
+        <v>4.239439E-06</v>
       </c>
       <c r="E21" s="2">
-        <v>0.0006464818</v>
+        <v>0.0005887113</v>
       </c>
     </row>
     <row r="22">
@@ -541,16 +541,16 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>0.0002486731</v>
+        <v>0.0002515044</v>
       </c>
       <c r="C22" s="2">
-        <v>0.0002352969</v>
+        <v>0.0002371008</v>
       </c>
       <c r="D22" s="2">
-        <v>4.29035E-06</v>
+        <v>4.31736E-06</v>
       </c>
       <c r="E22" s="2">
-        <v>0.0006222097</v>
+        <v>0.0005671218</v>
       </c>
     </row>
     <row r="23">
@@ -558,16 +558,16 @@
         <v>1.05</v>
       </c>
       <c r="B23" s="2">
-        <v>0.0002418128</v>
+        <v>0.0002445089</v>
       </c>
       <c r="C23" s="2">
-        <v>0.0002284018</v>
+        <v>0.0002301964</v>
       </c>
       <c r="D23" s="2">
-        <v>4.365631E-06</v>
+        <v>4.393467E-06</v>
       </c>
       <c r="E23" s="2">
-        <v>0.000600234</v>
+        <v>0.0005475539</v>
       </c>
     </row>
     <row r="24">
@@ -575,16 +575,16 @@
         <v>1.1</v>
       </c>
       <c r="B24" s="2">
-        <v>0.0002353983</v>
+        <v>0.0002379576</v>
       </c>
       <c r="C24" s="2">
-        <v>0.0002220175</v>
+        <v>0.0002237907</v>
       </c>
       <c r="D24" s="2">
-        <v>4.439209E-06</v>
+        <v>4.467843E-06</v>
       </c>
       <c r="E24" s="2">
-        <v>0.0005802318</v>
+        <v>0.0005297118</v>
       </c>
     </row>
     <row r="25">
@@ -592,16 +592,16 @@
         <v>1.15</v>
       </c>
       <c r="B25" s="2">
-        <v>0.0002293761</v>
+        <v>0.0002317966</v>
       </c>
       <c r="C25" s="2">
-        <v>0.0002160792</v>
+        <v>0.000217819</v>
       </c>
       <c r="D25" s="2">
-        <v>4.511165E-06</v>
+        <v>4.540564E-06</v>
       </c>
       <c r="E25" s="2">
-        <v>0.0005619315</v>
+        <v>0.0005133484</v>
       </c>
     </row>
     <row r="26">
@@ -609,16 +609,16 @@
         <v>1.2</v>
       </c>
       <c r="B26" s="2">
-        <v>0.0002237015</v>
+        <v>0.0002259808</v>
       </c>
       <c r="C26" s="2">
-        <v>0.0002105322</v>
+        <v>0.0002122268</v>
       </c>
       <c r="D26" s="2">
-        <v>4.581571E-06</v>
+        <v>4.6117E-06</v>
       </c>
       <c r="E26" s="2">
-        <v>0.0005451047</v>
+        <v>0.0004982583</v>
       </c>
     </row>
     <row r="27">
@@ -626,16 +626,16 @@
         <v>1.25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.0002183355</v>
+        <v>0.0002204722</v>
       </c>
       <c r="C27" s="2">
-        <v>0.0002053291</v>
+        <v>0.0002069685</v>
       </c>
       <c r="D27" s="2">
-        <v>4.650493E-06</v>
+        <v>4.681316E-06</v>
       </c>
       <c r="E27" s="2">
-        <v>0.0005295548</v>
+        <v>0.0004842706</v>
       </c>
     </row>
     <row r="28">
@@ -643,16 +643,16 @@
         <v>1.3</v>
       </c>
       <c r="B28" s="2">
-        <v>0.0002132457</v>
+        <v>0.0002152391</v>
       </c>
       <c r="C28" s="2">
-        <v>0.0002004304</v>
+        <v>0.0002020062</v>
       </c>
       <c r="D28" s="2">
-        <v>4.717994E-06</v>
+        <v>4.749469E-06</v>
       </c>
       <c r="E28" s="2">
-        <v>0.0005151189</v>
+        <v>0.0004712439</v>
       </c>
     </row>
     <row r="29">
@@ -660,16 +660,16 @@
         <v>1.35</v>
       </c>
       <c r="B29" s="2">
-        <v>0.0002084044</v>
+        <v>0.0002102545</v>
       </c>
       <c r="C29" s="2">
-        <v>0.0001958026</v>
+        <v>0.0001973077</v>
       </c>
       <c r="D29" s="2">
-        <v>4.784128E-06</v>
+        <v>4.816216E-06</v>
       </c>
       <c r="E29" s="2">
-        <v>0.0005016589</v>
+        <v>0.0004590588</v>
       </c>
     </row>
     <row r="30">
@@ -677,16 +677,16 @@
         <v>1.4</v>
       </c>
       <c r="B30" s="2">
-        <v>0.0002037876</v>
+        <v>0.0002054954</v>
       </c>
       <c r="C30" s="2">
-        <v>0.0001914168</v>
+        <v>0.0001928458</v>
       </c>
       <c r="D30" s="2">
-        <v>4.848947E-06</v>
+        <v>4.881609E-06</v>
       </c>
       <c r="E30" s="2">
-        <v>0.0004890578</v>
+        <v>0.0004476152</v>
       </c>
     </row>
     <row r="31">
@@ -694,16 +694,16 @@
         <v>1.45</v>
       </c>
       <c r="B31" s="2">
-        <v>0.0001993748</v>
+        <v>0.0002009419</v>
       </c>
       <c r="C31" s="2">
-        <v>0.0001872487</v>
+        <v>0.0001885969</v>
       </c>
       <c r="D31" s="2">
-        <v>4.912501E-06</v>
+        <v>4.945696E-06</v>
       </c>
       <c r="E31" s="2">
-        <v>0.0004772163</v>
+        <v>0.0004368266</v>
       </c>
     </row>
     <row r="32">
@@ -711,16 +711,16 @@
         <v>1.5</v>
       </c>
       <c r="B32" s="2">
-        <v>0.0001951485</v>
+        <v>0.000196577</v>
       </c>
       <c r="C32" s="2">
-        <v>0.0001832771</v>
+        <v>0.0001845411</v>
       </c>
       <c r="D32" s="2">
-        <v>4.974834E-06</v>
+        <v>5.008521E-06</v>
       </c>
       <c r="E32" s="2">
-        <v>0.0004660492</v>
+        <v>0.0004266213</v>
       </c>
     </row>
     <row r="33">
@@ -728,16 +728,16 @@
         <v>1.55</v>
       </c>
       <c r="B33" s="2">
-        <v>0.0001910933</v>
+        <v>0.0001923855</v>
       </c>
       <c r="C33" s="2">
-        <v>0.0001794838</v>
+        <v>0.000180661</v>
       </c>
       <c r="D33" s="2">
-        <v>5.035988E-06</v>
+        <v>5.070128E-06</v>
       </c>
       <c r="E33" s="2">
-        <v>0.0004554835</v>
+        <v>0.0004169357</v>
       </c>
     </row>
     <row r="34">
@@ -745,16 +745,16 @@
         <v>1.6</v>
       </c>
       <c r="B34" s="2">
-        <v>0.0001871959</v>
+        <v>0.000188355</v>
       </c>
       <c r="C34" s="2">
-        <v>0.0001758529</v>
+        <v>0.000176942</v>
       </c>
       <c r="D34" s="2">
-        <v>5.096003E-06</v>
+        <v>5.130559E-06</v>
       </c>
       <c r="E34" s="2">
-        <v>0.0004454561</v>
+        <v>0.0004077191</v>
       </c>
     </row>
     <row r="35">
@@ -762,16 +762,16 @@
         <v>1.65</v>
       </c>
       <c r="B35" s="2">
-        <v>0.0001834445</v>
+        <v>0.000184474</v>
       </c>
       <c r="C35" s="2">
-        <v>0.0001723709</v>
+        <v>0.0001733711</v>
       </c>
       <c r="D35" s="2">
-        <v>5.154917E-06</v>
+        <v>5.189851E-06</v>
       </c>
       <c r="E35" s="2">
-        <v>0.0004359139</v>
+        <v>0.0003989251</v>
       </c>
     </row>
     <row r="36">
@@ -779,16 +779,16 @@
         <v>1.7</v>
       </c>
       <c r="B36" s="2">
-        <v>0.0001798292</v>
+        <v>0.000180733</v>
       </c>
       <c r="C36" s="2">
-        <v>0.000169026</v>
+        <v>0.0001699376</v>
       </c>
       <c r="D36" s="2">
-        <v>5.212765E-06</v>
+        <v>5.24804E-06</v>
       </c>
       <c r="E36" s="2">
-        <v>0.0004268108</v>
+        <v>0.0003905171</v>
       </c>
     </row>
     <row r="37">
@@ -796,16 +796,16 @@
         <v>1.75</v>
       </c>
       <c r="B37" s="2">
-        <v>0.0001763409</v>
+        <v>0.0001771235</v>
       </c>
       <c r="C37" s="2">
-        <v>0.000165808</v>
+        <v>0.000166632</v>
       </c>
       <c r="D37" s="2">
-        <v>5.26958E-06</v>
+        <v>5.305163E-06</v>
       </c>
       <c r="E37" s="2">
-        <v>0.0004181074</v>
+        <v>0.0003824622</v>
       </c>
     </row>
     <row r="38">
@@ -813,16 +813,16 @@
         <v>1.8</v>
       </c>
       <c r="B38" s="2">
-        <v>0.000172972</v>
+        <v>0.0001736381</v>
       </c>
       <c r="C38" s="2">
-        <v>0.0001627079</v>
+        <v>0.0001634461</v>
       </c>
       <c r="D38" s="2">
-        <v>5.325395E-06</v>
+        <v>5.361253E-06</v>
       </c>
       <c r="E38" s="2">
-        <v>0.0004097699</v>
+        <v>0.000374733</v>
       </c>
     </row>
     <row r="39">
@@ -830,16 +830,16 @@
         <v>1.85</v>
       </c>
       <c r="B39" s="2">
-        <v>0.0001697153</v>
+        <v>0.0001702701</v>
       </c>
       <c r="C39" s="2">
-        <v>0.000159718</v>
+        <v>0.0001603725</v>
       </c>
       <c r="D39" s="2">
-        <v>5.38024E-06</v>
+        <v>5.416342E-06</v>
       </c>
       <c r="E39" s="2">
-        <v>0.0004017683</v>
+        <v>0.000367305</v>
       </c>
     </row>
     <row r="40">
@@ -847,16 +847,16 @@
         <v>1.9</v>
       </c>
       <c r="B40" s="2">
-        <v>0.0001665649</v>
+        <v>0.0001670136</v>
       </c>
       <c r="C40" s="2">
-        <v>0.0001568313</v>
+        <v>0.0001574049</v>
       </c>
       <c r="D40" s="2">
-        <v>5.434144E-06</v>
+        <v>5.47046E-06</v>
       </c>
       <c r="E40" s="2">
-        <v>0.0003940775</v>
+        <v>0.0003601572</v>
       </c>
     </row>
     <row r="41">
@@ -864,16 +864,16 @@
         <v>1.95</v>
       </c>
       <c r="B41" s="2">
-        <v>0.0001635148</v>
+        <v>0.0001638629</v>
       </c>
       <c r="C41" s="2">
-        <v>0.0001540413</v>
+        <v>0.0001545371</v>
       </c>
       <c r="D41" s="2">
-        <v>5.487135E-06</v>
+        <v>5.523638E-06</v>
       </c>
       <c r="E41" s="2">
-        <v>0.0003866734</v>
+        <v>0.0003532706</v>
       </c>
     </row>
     <row r="42">
@@ -881,16 +881,16 @@
         <v>2</v>
       </c>
       <c r="B42" s="2">
-        <v>0.0001605604</v>
+        <v>0.0001608132</v>
       </c>
       <c r="C42" s="2">
-        <v>0.000151343</v>
+        <v>0.0001517643</v>
       </c>
       <c r="D42" s="2">
-        <v>5.53924E-06</v>
+        <v>5.575903E-06</v>
       </c>
       <c r="E42" s="2">
-        <v>0.0003795377</v>
+        <v>0.0003466292</v>
       </c>
     </row>
     <row r="43">
@@ -898,16 +898,16 @@
         <v>2.25</v>
       </c>
       <c r="B43" s="2">
-        <v>0.0001470751</v>
+        <v>0.0001469349</v>
       </c>
       <c r="C43" s="2">
-        <v>0.0001390661</v>
+        <v>0.0001391729</v>
       </c>
       <c r="D43" s="2">
-        <v>5.787347E-06</v>
+        <v>5.824478E-06</v>
       </c>
       <c r="E43" s="2">
-        <v>0.0003473183</v>
+        <v>0.0003166385</v>
       </c>
     </row>
     <row r="44">
@@ -915,16 +915,16 @@
         <v>2.5</v>
       </c>
       <c r="B44" s="2">
-        <v>0.0001354406</v>
+        <v>0.0001350392</v>
       </c>
       <c r="C44" s="2">
-        <v>0.0001285094</v>
+        <v>0.0001284025</v>
       </c>
       <c r="D44" s="2">
-        <v>6.016799E-06</v>
+        <v>6.05399E-06</v>
       </c>
       <c r="E44" s="2">
-        <v>0.000319849</v>
+        <v>0.0002911405</v>
       </c>
     </row>
     <row r="45">
@@ -932,16 +932,16 @@
         <v>2.75</v>
       </c>
       <c r="B45" s="2">
-        <v>0.0001253539</v>
+        <v>0.0001248044</v>
       </c>
       <c r="C45" s="2">
-        <v>0.0001193711</v>
+        <v>0.0001191426</v>
       </c>
       <c r="D45" s="2">
-        <v>6.230039E-06</v>
+        <v>6.267063E-06</v>
       </c>
       <c r="E45" s="2">
-        <v>0.0002961816</v>
+        <v>0.0002692895</v>
       </c>
     </row>
     <row r="46">
@@ -949,16 +949,16 @@
         <v>3</v>
       </c>
       <c r="B46" s="2">
-        <v>0.0001165829</v>
+        <v>0.0001159772</v>
       </c>
       <c r="C46" s="2">
-        <v>0.0001114283</v>
+        <v>0.0001111555</v>
       </c>
       <c r="D46" s="2">
-        <v>6.429163E-06</v>
+        <v>6.465938E-06</v>
       </c>
       <c r="E46" s="2">
-        <v>0.0002756614</v>
+        <v>0.0002504716</v>
       </c>
     </row>
     <row r="47">
@@ -966,16 +966,16 @@
         <v>3.25</v>
       </c>
       <c r="B47" s="2">
-        <v>0.0001089421</v>
+        <v>0.0001083546</v>
       </c>
       <c r="C47" s="2">
-        <v>0.0001045078</v>
+        <v>0.0001042554</v>
       </c>
       <c r="D47" s="2">
-        <v>6.615975E-06</v>
+        <v>6.65253E-06</v>
       </c>
       <c r="E47" s="2">
-        <v>0.0002578057</v>
+        <v>0.0002342318</v>
       </c>
     </row>
     <row r="48">
@@ -983,16 +983,16 @@
         <v>3.5</v>
       </c>
       <c r="B48" s="2">
-        <v>0.0001022802</v>
+        <v>0.0001017665</v>
       </c>
       <c r="C48" s="2">
-        <v>9.847182E-05</v>
+        <v>9.82881E-05</v>
       </c>
       <c r="D48" s="2">
-        <v>6.792032E-06</v>
+        <v>6.828486E-06</v>
       </c>
       <c r="E48" s="2">
-        <v>0.0002422486</v>
+        <v>0.0002202006</v>
       </c>
     </row>
     <row r="49">
@@ -1000,16 +1000,16 @@
         <v>3.75</v>
       </c>
       <c r="B49" s="2">
-        <v>9.646681E-05</v>
+        <v>9.60669E-05</v>
       </c>
       <c r="C49" s="2">
-        <v>9.320167E-05</v>
+        <v>9.312161E-05</v>
       </c>
       <c r="D49" s="2">
-        <v>6.958689E-06</v>
+        <v>6.99522E-06</v>
       </c>
       <c r="E49" s="2">
-        <v>0.000228677</v>
+        <v>0.0002080623</v>
       </c>
     </row>
     <row r="50">
@@ -1017,16 +1017,16 @@
         <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>9.138869E-05</v>
+        <v>9.113063E-05</v>
       </c>
       <c r="C50" s="2">
-        <v>8.859455E-05</v>
+        <v>8.864266E-05</v>
       </c>
       <c r="D50" s="2">
-        <v>7.117121E-06</v>
+        <v>7.153948E-06</v>
       </c>
       <c r="E50" s="2">
-        <v>0.0002168202</v>
+        <v>0.0001975466</v>
       </c>
     </row>
     <row r="51">
@@ -1034,16 +1034,16 @@
         <v>4.25</v>
       </c>
       <c r="B51" s="2">
-        <v>8.694921E-05</v>
+        <v>8.685021E-05</v>
       </c>
       <c r="C51" s="2">
-        <v>8.456326E-05</v>
+        <v>8.475424E-05</v>
       </c>
       <c r="D51" s="2">
-        <v>7.268348E-06</v>
+        <v>7.30572E-06</v>
       </c>
       <c r="E51" s="2">
-        <v>0.000206452</v>
+        <v>0.0001884228</v>
       </c>
     </row>
     <row r="52">
@@ -1051,16 +1051,16 @@
         <v>4.5</v>
       </c>
       <c r="B52" s="2">
-        <v>8.306449E-05</v>
+        <v>8.313412E-05</v>
       </c>
       <c r="C52" s="2">
-        <v>8.103219E-05</v>
+        <v>8.1374E-05</v>
       </c>
       <c r="D52" s="2">
-        <v>7.413258E-06</v>
+        <v>7.451437E-06</v>
       </c>
       <c r="E52" s="2">
-        <v>0.0001973764</v>
+        <v>0.0001804964</v>
       </c>
     </row>
     <row r="53">
@@ -1068,16 +1068,16 @@
         <v>4.75</v>
       </c>
       <c r="B53" s="2">
-        <v>7.966179E-05</v>
+        <v>7.990433E-05</v>
       </c>
       <c r="C53" s="2">
-        <v>7.793577E-05</v>
+        <v>7.843196E-05</v>
       </c>
       <c r="D53" s="2">
-        <v>7.55262E-06</v>
+        <v>7.591873E-06</v>
       </c>
       <c r="E53" s="2">
-        <v>0.0001894238</v>
+        <v>0.0001736036</v>
       </c>
     </row>
     <row r="54">
@@ -1085,16 +1085,16 @@
         <v>5</v>
       </c>
       <c r="B54" s="2">
-        <v>7.667806E-05</v>
+        <v>7.709348E-05</v>
       </c>
       <c r="C54" s="2">
-        <v>7.521721E-05</v>
+        <v>7.586757E-05</v>
       </c>
       <c r="D54" s="2">
-        <v>7.687107E-06</v>
+        <v>7.727697E-06</v>
       </c>
       <c r="E54" s="2">
-        <v>0.0001824471</v>
+        <v>0.0001676019</v>
       </c>
     </row>
     <row r="55">
@@ -1102,16 +1102,16 @@
         <v>5.25</v>
       </c>
       <c r="B55" s="2">
-        <v>7.405871E-05</v>
+        <v>7.464305E-05</v>
       </c>
       <c r="C55" s="2">
-        <v>7.282726E-05</v>
+        <v>7.362809E-05</v>
       </c>
       <c r="D55" s="2">
-        <v>7.817294E-06</v>
+        <v>7.859484E-06</v>
       </c>
       <c r="E55" s="2">
-        <v>0.0001763191</v>
+        <v>0.0001623661</v>
       </c>
     </row>
     <row r="56">
@@ -1119,16 +1119,16 @@
         <v>5.5</v>
       </c>
       <c r="B56" s="2">
-        <v>7.17561E-05</v>
+        <v>7.250278E-05</v>
       </c>
       <c r="C56" s="2">
-        <v>7.072304E-05</v>
+        <v>7.166816E-05</v>
       </c>
       <c r="D56" s="2">
-        <v>7.943691E-06</v>
+        <v>7.987729E-06</v>
       </c>
       <c r="E56" s="2">
-        <v>0.0001709284</v>
+        <v>0.0001577888</v>
       </c>
     </row>
     <row r="57">
@@ -1136,16 +1136,16 @@
         <v>5.75</v>
       </c>
       <c r="B57" s="2">
-        <v>6.972891E-05</v>
+        <v>7.062975E-05</v>
       </c>
       <c r="C57" s="2">
-        <v>6.886729E-05</v>
+        <v>6.994922E-05</v>
       </c>
       <c r="D57" s="2">
-        <v>8.066738E-06</v>
+        <v>8.11286E-06</v>
       </c>
       <c r="E57" s="2">
-        <v>0.000166179</v>
+        <v>0.0001537791</v>
       </c>
     </row>
     <row r="58">
@@ -1153,16 +1153,16 @@
         <v>6</v>
       </c>
       <c r="B58" s="2">
-        <v>6.794128E-05</v>
+        <v>6.898718E-05</v>
       </c>
       <c r="C58" s="2">
-        <v>6.722774E-05</v>
+        <v>6.843824E-05</v>
       </c>
       <c r="D58" s="2">
-        <v>8.186818E-06</v>
+        <v>8.235246E-06</v>
       </c>
       <c r="E58" s="2">
-        <v>0.0001619874</v>
+        <v>0.0001502595</v>
       </c>
     </row>
     <row r="59">
@@ -1170,16 +1170,16 @@
         <v>6.25</v>
       </c>
       <c r="B59" s="2">
-        <v>6.636202E-05</v>
+        <v>6.754328E-05</v>
       </c>
       <c r="C59" s="2">
-        <v>6.577629E-05</v>
+        <v>6.710659E-05</v>
       </c>
       <c r="D59" s="2">
-        <v>8.304267E-06</v>
+        <v>8.355204E-06</v>
       </c>
       <c r="E59" s="2">
-        <v>0.0001582812</v>
+        <v>0.0001471622</v>
       </c>
     </row>
     <row r="60">
@@ -1187,16 +1187,16 @@
         <v>6.5</v>
       </c>
       <c r="B60" s="2">
-        <v>6.496387E-05</v>
+        <v>6.627075E-05</v>
       </c>
       <c r="C60" s="2">
-        <v>6.448841E-05</v>
+        <v>6.592969E-05</v>
       </c>
       <c r="D60" s="2">
-        <v>8.419378E-06</v>
+        <v>8.473007E-06</v>
       </c>
       <c r="E60" s="2">
-        <v>0.0001549968</v>
+        <v>0.0001444294</v>
       </c>
     </row>
     <row r="61">
@@ -1204,16 +1204,16 @@
         <v>6.75</v>
       </c>
       <c r="B61" s="2">
-        <v>6.372359E-05</v>
+        <v>6.514595E-05</v>
       </c>
       <c r="C61" s="2">
-        <v>6.334316E-05</v>
+        <v>6.488623E-05</v>
       </c>
       <c r="D61" s="2">
-        <v>8.5324E-06</v>
+        <v>8.588894E-06</v>
       </c>
       <c r="E61" s="2">
-        <v>0.0001520803</v>
+        <v>0.0001420106</v>
       </c>
     </row>
     <row r="62">
@@ -1221,16 +1221,16 @@
         <v>7</v>
       </c>
       <c r="B62" s="2">
-        <v>6.262078E-05</v>
+        <v>6.414899E-05</v>
       </c>
       <c r="C62" s="2">
-        <v>6.232216E-05</v>
+        <v>6.395839E-05</v>
       </c>
       <c r="D62" s="2">
-        <v>8.643556E-06</v>
+        <v>8.703067E-06</v>
       </c>
       <c r="E62" s="2">
-        <v>0.0001494841</v>
+        <v>0.0001398639</v>
       </c>
     </row>
     <row r="63">
@@ -1238,16 +1238,16 @@
         <v>7.25</v>
       </c>
       <c r="B63" s="2">
-        <v>6.163794E-05</v>
+        <v>6.326195E-05</v>
       </c>
       <c r="C63" s="2">
-        <v>6.140964E-05</v>
+        <v>6.312991E-05</v>
       </c>
       <c r="D63" s="2">
-        <v>8.753034E-06</v>
+        <v>8.815705E-06</v>
       </c>
       <c r="E63" s="2">
-        <v>0.0001471676</v>
+        <v>0.0001379506</v>
       </c>
     </row>
     <row r="64">
@@ -1255,16 +1255,16 @@
         <v>7.5</v>
       </c>
       <c r="B64" s="2">
-        <v>6.075983E-05</v>
+        <v>6.247023E-05</v>
       </c>
       <c r="C64" s="2">
-        <v>6.059188E-05</v>
+        <v>6.238773E-05</v>
       </c>
       <c r="D64" s="2">
-        <v>8.861003E-06</v>
+        <v>8.926961E-06</v>
       </c>
       <c r="E64" s="2">
-        <v>0.0001450952</v>
+        <v>0.0001362401</v>
       </c>
     </row>
     <row r="65">
@@ -1272,16 +1272,16 @@
         <v>7.75</v>
       </c>
       <c r="B65" s="2">
-        <v>5.997306E-05</v>
+        <v>6.176063E-05</v>
       </c>
       <c r="C65" s="2">
-        <v>5.98568E-05</v>
+        <v>6.171993E-05</v>
       </c>
       <c r="D65" s="2">
-        <v>8.967608E-06</v>
+        <v>9.036969E-06</v>
       </c>
       <c r="E65" s="2">
-        <v>0.0001432357</v>
+        <v>0.0001347042</v>
       </c>
     </row>
     <row r="66">
@@ -1289,16 +1289,16 @@
         <v>8</v>
       </c>
       <c r="B66" s="2">
-        <v>5.926585E-05</v>
+        <v>6.112229E-05</v>
       </c>
       <c r="C66" s="2">
-        <v>5.919382E-05</v>
+        <v>6.111678E-05</v>
       </c>
       <c r="D66" s="2">
-        <v>9.072979E-06</v>
+        <v>9.145843E-06</v>
       </c>
       <c r="E66" s="2">
-        <v>0.0001415619</v>
+        <v>0.0001333201</v>
       </c>
     </row>
     <row r="67">
@@ -1306,16 +1306,16 @@
         <v>8.25</v>
       </c>
       <c r="B67" s="2">
-        <v>5.862812E-05</v>
+        <v>6.054572E-05</v>
       </c>
       <c r="C67" s="2">
-        <v>5.859384E-05</v>
+        <v>6.056971E-05</v>
       </c>
       <c r="D67" s="2">
-        <v>9.177228E-06</v>
+        <v>9.253684E-06</v>
       </c>
       <c r="E67" s="2">
-        <v>0.0001400502</v>
+        <v>0.0001320678</v>
       </c>
     </row>
     <row r="68">
@@ -1323,16 +1323,16 @@
         <v>8.5</v>
       </c>
       <c r="B68" s="2">
-        <v>5.805085E-05</v>
+        <v>6.002276E-05</v>
       </c>
       <c r="C68" s="2">
-        <v>5.804871E-05</v>
+        <v>6.007141E-05</v>
       </c>
       <c r="D68" s="2">
-        <v>9.280457E-06</v>
+        <v>9.360577E-06</v>
       </c>
       <c r="E68" s="2">
-        <v>0.0001386796</v>
+        <v>0.0001309299</v>
       </c>
     </row>
     <row r="69">
@@ -1340,16 +1340,16 @@
         <v>8.75</v>
       </c>
       <c r="B69" s="2">
-        <v>5.752651E-05</v>
+        <v>5.954643E-05</v>
       </c>
       <c r="C69" s="2">
-        <v>5.755168E-05</v>
+        <v>5.961557E-05</v>
       </c>
       <c r="D69" s="2">
-        <v>9.382748E-06</v>
+        <v>9.466598E-06</v>
       </c>
       <c r="E69" s="2">
-        <v>0.0001374327</v>
+        <v>0.0001298915</v>
       </c>
     </row>
     <row r="70">
@@ -1357,16 +1357,16 @@
         <v>9</v>
       </c>
       <c r="B70" s="2">
-        <v>5.704845E-05</v>
+        <v>5.911069E-05</v>
       </c>
       <c r="C70" s="2">
-        <v>5.709673E-05</v>
+        <v>5.919675E-05</v>
       </c>
       <c r="D70" s="2">
-        <v>9.48418E-06</v>
+        <v>9.571812E-06</v>
       </c>
       <c r="E70" s="2">
-        <v>0.0001362938</v>
+        <v>0.0001289399</v>
       </c>
     </row>
     <row r="71">
@@ -1374,16 +1374,16 @@
         <v>9.25</v>
       </c>
       <c r="B71" s="2">
-        <v>5.6611E-05</v>
+        <v>5.871044E-05</v>
       </c>
       <c r="C71" s="2">
-        <v>5.667877E-05</v>
+        <v>5.881036E-05</v>
       </c>
       <c r="D71" s="2">
-        <v>9.584816E-06</v>
+        <v>9.676276E-06</v>
       </c>
       <c r="E71" s="2">
-        <v>0.00013525</v>
+        <v>0.0001280642</v>
       </c>
     </row>
     <row r="72">
@@ -1391,16 +1391,16 @@
         <v>9.5</v>
       </c>
       <c r="B72" s="2">
-        <v>5.620922E-05</v>
+        <v>5.834083E-05</v>
       </c>
       <c r="C72" s="2">
-        <v>5.629332E-05</v>
+        <v>5.845197E-05</v>
       </c>
       <c r="D72" s="2">
-        <v>9.684714E-06</v>
+        <v>9.780043E-06</v>
       </c>
       <c r="E72" s="2">
-        <v>0.0001342895</v>
+        <v>0.0001272537</v>
       </c>
     </row>
     <row r="73">
@@ -1408,16 +1408,16 @@
         <v>9.75</v>
       </c>
       <c r="B73" s="2">
-        <v>5.583881E-05</v>
+        <v>5.799855E-05</v>
       </c>
       <c r="C73" s="2">
-        <v>5.593651E-05</v>
+        <v>5.811867E-05</v>
       </c>
       <c r="D73" s="2">
-        <v>9.783925E-06</v>
+        <v>9.883152E-06</v>
       </c>
       <c r="E73" s="2">
-        <v>0.0001334025</v>
+        <v>0.000126502</v>
       </c>
     </row>
     <row r="74">
@@ -1425,16 +1425,16 @@
         <v>10</v>
       </c>
       <c r="B74" s="2">
-        <v>5.549615E-05</v>
+        <v>5.767981E-05</v>
       </c>
       <c r="C74" s="2">
-        <v>5.560509E-05</v>
+        <v>5.7807E-05</v>
       </c>
       <c r="D74" s="2">
-        <v>9.882492E-06</v>
+        <v>9.985645E-06</v>
       </c>
       <c r="E74" s="2">
-        <v>0.0001325805</v>
+        <v>0.0001258006</v>
       </c>
     </row>
     <row r="75">
@@ -1442,16 +1442,16 @@
         <v>10.25</v>
       </c>
       <c r="B75" s="2">
-        <v>5.517784E-05</v>
+        <v>5.738146E-05</v>
       </c>
       <c r="C75" s="2">
-        <v>5.529598E-05</v>
+        <v>5.75141E-05</v>
       </c>
       <c r="D75" s="2">
-        <v>9.980456E-06</v>
+        <v>1.008756E-05</v>
       </c>
       <c r="E75" s="2">
-        <v>0.0001318155</v>
+        <v>0.0001251427</v>
       </c>
     </row>
     <row r="76">
@@ -1459,16 +1459,16 @@
         <v>10.5</v>
       </c>
       <c r="B76" s="2">
-        <v>5.488087E-05</v>
+        <v>5.71016E-05</v>
       </c>
       <c r="C76" s="2">
-        <v>5.500646E-05</v>
+        <v>5.723829E-05</v>
       </c>
       <c r="D76" s="2">
-        <v>1.007785E-05</v>
+        <v>1.018892E-05</v>
       </c>
       <c r="E76" s="2">
-        <v>0.0001311006</v>
+        <v>0.0001245247</v>
       </c>
     </row>
     <row r="77">
@@ -1476,16 +1476,16 @@
         <v>10.75</v>
       </c>
       <c r="B77" s="2">
-        <v>5.460332E-05</v>
+        <v>5.683747E-05</v>
       </c>
       <c r="C77" s="2">
-        <v>5.47348E-05</v>
+        <v>5.697706E-05</v>
       </c>
       <c r="D77" s="2">
-        <v>1.017471E-05</v>
+        <v>1.028976E-05</v>
       </c>
       <c r="E77" s="2">
-        <v>0.0001304313</v>
+        <v>0.0001239404</v>
       </c>
     </row>
     <row r="78">
@@ -1493,16 +1493,16 @@
         <v>11</v>
       </c>
       <c r="B78" s="2">
-        <v>5.434244E-05</v>
+        <v>5.658748E-05</v>
       </c>
       <c r="C78" s="2">
-        <v>5.447851E-05</v>
+        <v>5.6729E-05</v>
       </c>
       <c r="D78" s="2">
-        <v>1.027106E-05</v>
+        <v>1.03901E-05</v>
       </c>
       <c r="E78" s="2">
-        <v>0.0001298013</v>
+        <v>0.0001233866</v>
       </c>
     </row>
     <row r="79">
@@ -1510,16 +1510,16 @@
         <v>11.25</v>
       </c>
       <c r="B79" s="2">
-        <v>5.409606E-05</v>
+        <v>5.635008E-05</v>
       </c>
       <c r="C79" s="2">
-        <v>5.423565E-05</v>
+        <v>5.649268E-05</v>
       </c>
       <c r="D79" s="2">
-        <v>1.036693E-05</v>
+        <v>1.048997E-05</v>
       </c>
       <c r="E79" s="2">
-        <v>0.0001292053</v>
+        <v>0.00012286</v>
       </c>
     </row>
     <row r="80">
@@ -1527,16 +1527,16 @@
         <v>11.5</v>
       </c>
       <c r="B80" s="2">
-        <v>5.386335E-05</v>
+        <v>5.612377E-05</v>
       </c>
       <c r="C80" s="2">
-        <v>5.400545E-05</v>
+        <v>5.626676E-05</v>
       </c>
       <c r="D80" s="2">
-        <v>1.046234E-05</v>
+        <v>1.058937E-05</v>
       </c>
       <c r="E80" s="2">
-        <v>0.0001286416</v>
+        <v>0.0001223574</v>
       </c>
     </row>
     <row r="81">
@@ -1544,16 +1544,16 @@
         <v>11.75</v>
       </c>
       <c r="B81" s="2">
-        <v>5.364219E-05</v>
+        <v>5.590754E-05</v>
       </c>
       <c r="C81" s="2">
-        <v>5.378599E-05</v>
+        <v>5.605032E-05</v>
       </c>
       <c r="D81" s="2">
-        <v>1.055731E-05</v>
+        <v>1.068834E-05</v>
       </c>
       <c r="E81" s="2">
-        <v>0.0001281051</v>
+        <v>0.0001218767</v>
       </c>
     </row>
     <row r="82">
@@ -1561,16 +1561,16 @@
         <v>12</v>
       </c>
       <c r="B82" s="2">
-        <v>5.343113E-05</v>
+        <v>5.570032E-05</v>
       </c>
       <c r="C82" s="2">
-        <v>5.357598E-05</v>
+        <v>5.584239E-05</v>
       </c>
       <c r="D82" s="2">
-        <v>1.065185E-05</v>
+        <v>1.078687E-05</v>
       </c>
       <c r="E82" s="2">
-        <v>0.0001275925</v>
+        <v>0.0001214155</v>
       </c>
     </row>
     <row r="83">
@@ -1578,16 +1578,16 @@
         <v>12.25</v>
       </c>
       <c r="B83" s="2">
-        <v>5.322968E-05</v>
+        <v>5.550128E-05</v>
       </c>
       <c r="C83" s="2">
-        <v>5.337496E-05</v>
+        <v>5.564222E-05</v>
       </c>
       <c r="D83" s="2">
-        <v>1.074599E-05</v>
+        <v>1.0885E-05</v>
       </c>
       <c r="E83" s="2">
-        <v>0.0001271026</v>
+        <v>0.000120972</v>
       </c>
     </row>
     <row r="84">
@@ -1595,16 +1595,16 @@
         <v>12.5</v>
       </c>
       <c r="B84" s="2">
-        <v>5.303656E-05</v>
+        <v>5.530966E-05</v>
       </c>
       <c r="C84" s="2">
-        <v>5.318176E-05</v>
+        <v>5.544911E-05</v>
       </c>
       <c r="D84" s="2">
-        <v>1.083974E-05</v>
+        <v>1.098272E-05</v>
       </c>
       <c r="E84" s="2">
-        <v>0.0001266325</v>
+        <v>0.0001205448</v>
       </c>
     </row>
     <row r="85">
@@ -1612,16 +1612,16 @@
         <v>12.75</v>
       </c>
       <c r="B85" s="2">
-        <v>5.285092E-05</v>
+        <v>5.512475E-05</v>
       </c>
       <c r="C85" s="2">
-        <v>5.299563E-05</v>
+        <v>5.526241E-05</v>
       </c>
       <c r="D85" s="2">
-        <v>1.093312E-05</v>
+        <v>1.108005E-05</v>
       </c>
       <c r="E85" s="2">
-        <v>0.0001261802</v>
+        <v>0.0001201321</v>
       </c>
     </row>
     <row r="86">
@@ -1629,16 +1629,16 @@
         <v>13</v>
       </c>
       <c r="B86" s="2">
-        <v>5.267225E-05</v>
+        <v>5.494606E-05</v>
       </c>
       <c r="C86" s="2">
-        <v>5.28161E-05</v>
+        <v>5.508167E-05</v>
       </c>
       <c r="D86" s="2">
-        <v>1.102612E-05</v>
+        <v>1.117701E-05</v>
       </c>
       <c r="E86" s="2">
-        <v>0.0001257444</v>
+        <v>0.000119733</v>
       </c>
     </row>
     <row r="87">
@@ -1646,16 +1646,16 @@
         <v>13.25</v>
       </c>
       <c r="B87" s="2">
-        <v>5.249989E-05</v>
+        <v>5.477298E-05</v>
       </c>
       <c r="C87" s="2">
-        <v>5.264257E-05</v>
+        <v>5.490636E-05</v>
       </c>
       <c r="D87" s="2">
-        <v>1.111877E-05</v>
+        <v>1.12736E-05</v>
       </c>
       <c r="E87" s="2">
-        <v>0.0001253237</v>
+        <v>0.0001193462</v>
       </c>
     </row>
     <row r="88">
@@ -1663,16 +1663,16 @@
         <v>13.5</v>
       </c>
       <c r="B88" s="2">
-        <v>5.233334E-05</v>
+        <v>5.460506E-05</v>
       </c>
       <c r="C88" s="2">
-        <v>5.247458E-05</v>
+        <v>5.473603E-05</v>
       </c>
       <c r="D88" s="2">
-        <v>1.121107E-05</v>
+        <v>1.136983E-05</v>
       </c>
       <c r="E88" s="2">
-        <v>0.0001249168</v>
+        <v>0.0001189707</v>
       </c>
     </row>
     <row r="89">
@@ -1680,16 +1680,16 @@
         <v>13.75</v>
       </c>
       <c r="B89" s="2">
-        <v>5.217214E-05</v>
+        <v>5.444195E-05</v>
       </c>
       <c r="C89" s="2">
-        <v>5.231171E-05</v>
+        <v>5.45704E-05</v>
       </c>
       <c r="D89" s="2">
-        <v>1.130303E-05</v>
+        <v>1.146571E-05</v>
       </c>
       <c r="E89" s="2">
-        <v>0.0001245227</v>
+        <v>0.0001186058</v>
       </c>
     </row>
     <row r="90">
@@ -1697,16 +1697,16 @@
         <v>14</v>
       </c>
       <c r="B90" s="2">
-        <v>5.201587E-05</v>
+        <v>5.428324E-05</v>
       </c>
       <c r="C90" s="2">
-        <v>5.215357E-05</v>
+        <v>5.440907E-05</v>
       </c>
       <c r="D90" s="2">
-        <v>1.139467E-05</v>
+        <v>1.156125E-05</v>
       </c>
       <c r="E90" s="2">
-        <v>0.0001241404</v>
+        <v>0.0001182506</v>
       </c>
     </row>
     <row r="91">
@@ -1714,16 +1714,16 @@
         <v>14.25</v>
       </c>
       <c r="B91" s="2">
-        <v>5.186418E-05</v>
+        <v>5.412867E-05</v>
       </c>
       <c r="C91" s="2">
-        <v>5.199986E-05</v>
+        <v>5.425181E-05</v>
       </c>
       <c r="D91" s="2">
-        <v>1.148598E-05</v>
+        <v>1.165645E-05</v>
       </c>
       <c r="E91" s="2">
-        <v>0.0001237691</v>
+        <v>0.0001179046</v>
       </c>
     </row>
     <row r="92">
@@ -1731,16 +1731,16 @@
         <v>14.5</v>
       </c>
       <c r="B92" s="2">
-        <v>5.171685E-05</v>
+        <v>5.397798E-05</v>
       </c>
       <c r="C92" s="2">
-        <v>5.185036E-05</v>
+        <v>5.409836E-05</v>
       </c>
       <c r="D92" s="2">
-        <v>1.157698E-05</v>
+        <v>1.175133E-05</v>
       </c>
       <c r="E92" s="2">
-        <v>0.0001234083</v>
+        <v>0.0001175671</v>
       </c>
     </row>
     <row r="93">
@@ -1748,16 +1748,16 @@
         <v>14.75</v>
       </c>
       <c r="B93" s="2">
-        <v>5.157348E-05</v>
+        <v>5.383091E-05</v>
       </c>
       <c r="C93" s="2">
-        <v>5.170471E-05</v>
+        <v>5.394852E-05</v>
       </c>
       <c r="D93" s="2">
-        <v>1.166767E-05</v>
+        <v>1.184588E-05</v>
       </c>
       <c r="E93" s="2">
-        <v>0.000123057</v>
+        <v>0.0001172377</v>
       </c>
     </row>
     <row r="94">
@@ -1765,16 +1765,16 @@
         <v>15</v>
       </c>
       <c r="B94" s="2">
-        <v>5.143368E-05</v>
+        <v>5.36873E-05</v>
       </c>
       <c r="C94" s="2">
-        <v>5.156257E-05</v>
+        <v>5.38021E-05</v>
       </c>
       <c r="D94" s="2">
-        <v>1.175806E-05</v>
+        <v>1.194013E-05</v>
       </c>
       <c r="E94" s="2">
-        <v>0.0001227143</v>
+        <v>0.0001169159</v>
       </c>
     </row>
     <row r="95">
@@ -1782,16 +1782,16 @@
         <v>15.25</v>
       </c>
       <c r="B95" s="2">
-        <v>5.129723E-05</v>
+        <v>5.354696E-05</v>
       </c>
       <c r="C95" s="2">
-        <v>5.142371E-05</v>
+        <v>5.365894E-05</v>
       </c>
       <c r="D95" s="2">
-        <v>1.184816E-05</v>
+        <v>1.203406E-05</v>
       </c>
       <c r="E95" s="2">
-        <v>0.0001223797</v>
+        <v>0.0001166015</v>
       </c>
     </row>
     <row r="96">
@@ -1799,16 +1799,16 @@
         <v>15.5</v>
       </c>
       <c r="B96" s="2">
-        <v>5.116426E-05</v>
+        <v>5.340974E-05</v>
       </c>
       <c r="C96" s="2">
-        <v>5.128826E-05</v>
+        <v>5.35189E-05</v>
       </c>
       <c r="D96" s="2">
-        <v>1.193796E-05</v>
+        <v>1.21277E-05</v>
       </c>
       <c r="E96" s="2">
-        <v>0.0001220536</v>
+        <v>0.0001162939</v>
       </c>
     </row>
     <row r="97">
@@ -1816,16 +1816,16 @@
         <v>15.75</v>
       </c>
       <c r="B97" s="2">
-        <v>5.103428E-05</v>
+        <v>5.32755E-05</v>
       </c>
       <c r="C97" s="2">
-        <v>5.115577E-05</v>
+        <v>5.338184E-05</v>
       </c>
       <c r="D97" s="2">
-        <v>1.202749E-05</v>
+        <v>1.222103E-05</v>
       </c>
       <c r="E97" s="2">
-        <v>0.0001217346</v>
+        <v>0.000115993</v>
       </c>
     </row>
     <row r="98">
@@ -1833,16 +1833,16 @@
         <v>16</v>
       </c>
       <c r="B98" s="2">
-        <v>5.090699E-05</v>
+        <v>5.31441E-05</v>
       </c>
       <c r="C98" s="2">
-        <v>5.102596E-05</v>
+        <v>5.324764E-05</v>
       </c>
       <c r="D98" s="2">
-        <v>1.211674E-05</v>
+        <v>1.231408E-05</v>
       </c>
       <c r="E98" s="2">
-        <v>0.0001214223</v>
+        <v>0.0001156984</v>
       </c>
     </row>
     <row r="99">
@@ -1850,16 +1850,16 @@
         <v>16.25</v>
       </c>
       <c r="B99" s="2">
-        <v>5.078225E-05</v>
+        <v>5.301543E-05</v>
       </c>
       <c r="C99" s="2">
-        <v>5.08987E-05</v>
+        <v>5.311619E-05</v>
       </c>
       <c r="D99" s="2">
-        <v>1.220572E-05</v>
+        <v>1.240684E-05</v>
       </c>
       <c r="E99" s="2">
-        <v>0.0001211161</v>
+        <v>0.0001154099</v>
       </c>
     </row>
     <row r="100">
@@ -1867,16 +1867,16 @@
         <v>16.5</v>
       </c>
       <c r="B100" s="2">
-        <v>5.066027E-05</v>
+        <v>5.28894E-05</v>
       </c>
       <c r="C100" s="2">
-        <v>5.077418E-05</v>
+        <v>5.29874E-05</v>
       </c>
       <c r="D100" s="2">
-        <v>1.229443E-05</v>
+        <v>1.249932E-05</v>
       </c>
       <c r="E100" s="2">
-        <v>0.0001208167</v>
+        <v>0.0001151274</v>
       </c>
     </row>
     <row r="101">
@@ -1884,16 +1884,16 @@
         <v>16.75</v>
       </c>
       <c r="B101" s="2">
-        <v>5.054067E-05</v>
+        <v>5.276592E-05</v>
       </c>
       <c r="C101" s="2">
-        <v>5.065206E-05</v>
+        <v>5.286119E-05</v>
       </c>
       <c r="D101" s="2">
-        <v>1.238288E-05</v>
+        <v>1.259152E-05</v>
       </c>
       <c r="E101" s="2">
-        <v>0.000120523</v>
+        <v>0.0001148505</v>
       </c>
     </row>
     <row r="102">
@@ -1901,16 +1901,16 @@
         <v>17</v>
       </c>
       <c r="B102" s="2">
-        <v>5.042331E-05</v>
+        <v>5.264487E-05</v>
       </c>
       <c r="C102" s="2">
-        <v>5.05322E-05</v>
+        <v>5.273745E-05</v>
       </c>
       <c r="D102" s="2">
-        <v>1.247108E-05</v>
+        <v>1.268345E-05</v>
       </c>
       <c r="E102" s="2">
-        <v>0.0001202349</v>
+        <v>0.0001145791</v>
       </c>
     </row>
     <row r="103">
@@ -1918,16 +1918,16 @@
         <v>17.25</v>
       </c>
       <c r="B103" s="2">
-        <v>5.030811E-05</v>
+        <v>5.252613E-05</v>
       </c>
       <c r="C103" s="2">
-        <v>5.041452E-05</v>
+        <v>5.261605E-05</v>
       </c>
       <c r="D103" s="2">
-        <v>1.255902E-05</v>
+        <v>1.277511E-05</v>
       </c>
       <c r="E103" s="2">
-        <v>0.000119952</v>
+        <v>0.0001143128</v>
       </c>
     </row>
     <row r="104">
@@ -1935,16 +1935,16 @@
         <v>17.5</v>
       </c>
       <c r="B104" s="2">
-        <v>5.019513E-05</v>
+        <v>5.240971E-05</v>
       </c>
       <c r="C104" s="2">
-        <v>5.029907E-05</v>
+        <v>5.249701E-05</v>
       </c>
       <c r="D104" s="2">
-        <v>1.264671E-05</v>
+        <v>1.286651E-05</v>
       </c>
       <c r="E104" s="2">
-        <v>0.0001196746</v>
+        <v>0.0001140517</v>
       </c>
     </row>
     <row r="105">
@@ -1952,16 +1952,16 @@
         <v>17.75</v>
       </c>
       <c r="B105" s="2">
-        <v>5.008423E-05</v>
+        <v>5.229552E-05</v>
       </c>
       <c r="C105" s="2">
-        <v>5.018574E-05</v>
+        <v>5.238023E-05</v>
       </c>
       <c r="D105" s="2">
-        <v>1.273415E-05</v>
+        <v>1.295765E-05</v>
       </c>
       <c r="E105" s="2">
-        <v>0.0001194023</v>
+        <v>0.0001137957</v>
       </c>
     </row>
     <row r="106">
@@ -1969,16 +1969,16 @@
         <v>18</v>
       </c>
       <c r="B106" s="2">
-        <v>4.997536E-05</v>
+        <v>5.218346E-05</v>
       </c>
       <c r="C106" s="2">
-        <v>5.007446E-05</v>
+        <v>5.226563E-05</v>
       </c>
       <c r="D106" s="2">
-        <v>1.282136E-05</v>
+        <v>1.304854E-05</v>
       </c>
       <c r="E106" s="2">
-        <v>0.0001191349</v>
+        <v>0.0001135444</v>
       </c>
     </row>
     <row r="107">
@@ -1986,16 +1986,16 @@
         <v>18.25</v>
       </c>
       <c r="B107" s="2">
-        <v>4.986847E-05</v>
+        <v>5.207343E-05</v>
       </c>
       <c r="C107" s="2">
-        <v>4.996519E-05</v>
+        <v>5.215312E-05</v>
       </c>
       <c r="D107" s="2">
-        <v>1.290833E-05</v>
+        <v>1.313918E-05</v>
       </c>
       <c r="E107" s="2">
-        <v>0.0001188724</v>
+        <v>0.0001132978</v>
       </c>
     </row>
     <row r="108">
@@ -2003,16 +2003,16 @@
         <v>18.5</v>
       </c>
       <c r="B108" s="2">
-        <v>4.97635E-05</v>
+        <v>5.196545E-05</v>
       </c>
       <c r="C108" s="2">
-        <v>4.985787E-05</v>
+        <v>5.204269E-05</v>
       </c>
       <c r="D108" s="2">
-        <v>1.299506E-05</v>
+        <v>1.322957E-05</v>
       </c>
       <c r="E108" s="2">
-        <v>0.0001186147</v>
+        <v>0.0001130557</v>
       </c>
     </row>
     <row r="109">
@@ -2020,16 +2020,16 @@
         <v>18.75</v>
       </c>
       <c r="B109" s="2">
-        <v>4.966043E-05</v>
+        <v>5.185946E-05</v>
       </c>
       <c r="C109" s="2">
-        <v>4.975247E-05</v>
+        <v>5.193431E-05</v>
       </c>
       <c r="D109" s="2">
-        <v>1.308156E-05</v>
+        <v>1.331972E-05</v>
       </c>
       <c r="E109" s="2">
-        <v>0.0001183615</v>
+        <v>0.0001128181</v>
       </c>
     </row>
     <row r="110">
@@ -2037,16 +2037,16 @@
         <v>19</v>
       </c>
       <c r="B110" s="2">
-        <v>4.95592E-05</v>
+        <v>5.17554E-05</v>
       </c>
       <c r="C110" s="2">
-        <v>4.964895E-05</v>
+        <v>5.182789E-05</v>
       </c>
       <c r="D110" s="2">
-        <v>1.316784E-05</v>
+        <v>1.340963E-05</v>
       </c>
       <c r="E110" s="2">
-        <v>0.0001181129</v>
+        <v>0.0001125848</v>
       </c>
     </row>
     <row r="111">
@@ -2054,16 +2054,16 @@
         <v>19.25</v>
       </c>
       <c r="B111" s="2">
-        <v>4.94598E-05</v>
+        <v>5.16532E-05</v>
       </c>
       <c r="C111" s="2">
-        <v>4.954728E-05</v>
+        <v>5.172339E-05</v>
       </c>
       <c r="D111" s="2">
-        <v>1.325389E-05</v>
+        <v>1.349931E-05</v>
       </c>
       <c r="E111" s="2">
-        <v>0.0001178688</v>
+        <v>0.0001123557</v>
       </c>
     </row>
     <row r="112">
@@ -2071,16 +2071,16 @@
         <v>19.5</v>
       </c>
       <c r="B112" s="2">
-        <v>4.936214E-05</v>
+        <v>5.155285E-05</v>
       </c>
       <c r="C112" s="2">
-        <v>4.94474E-05</v>
+        <v>5.162078E-05</v>
       </c>
       <c r="D112" s="2">
-        <v>1.333972E-05</v>
+        <v>1.358876E-05</v>
       </c>
       <c r="E112" s="2">
-        <v>0.000117629</v>
+        <v>0.0001121308</v>
       </c>
     </row>
     <row r="113">
@@ -2088,16 +2088,16 @@
         <v>19.75</v>
       </c>
       <c r="B113" s="2">
-        <v>4.92662E-05</v>
+        <v>5.145431E-05</v>
       </c>
       <c r="C113" s="2">
-        <v>4.934926E-05</v>
+        <v>5.152003E-05</v>
       </c>
       <c r="D113" s="2">
-        <v>1.342533E-05</v>
+        <v>1.367797E-05</v>
       </c>
       <c r="E113" s="2">
-        <v>0.0001173934</v>
+        <v>0.00011191</v>
       </c>
     </row>
     <row r="114">
@@ -2105,16 +2105,16 @@
         <v>20</v>
       </c>
       <c r="B114" s="2">
-        <v>4.917191E-05</v>
+        <v>5.135754E-05</v>
       </c>
       <c r="C114" s="2">
-        <v>4.92528E-05</v>
+        <v>5.142109E-05</v>
       </c>
       <c r="D114" s="2">
-        <v>1.351073E-05</v>
+        <v>1.376697E-05</v>
       </c>
       <c r="E114" s="2">
-        <v>0.0001171619</v>
+        <v>0.0001116931</v>
       </c>
     </row>
     <row r="115">
@@ -2122,16 +2122,16 @@
         <v>20.25</v>
       </c>
       <c r="B115" s="2">
-        <v>4.907924E-05</v>
+        <v>5.126251E-05</v>
       </c>
       <c r="C115" s="2">
-        <v>4.9158E-05</v>
+        <v>5.132393E-05</v>
       </c>
       <c r="D115" s="2">
-        <v>1.359592E-05</v>
+        <v>1.385574E-05</v>
       </c>
       <c r="E115" s="2">
-        <v>0.0001169343</v>
+        <v>0.0001114802</v>
       </c>
     </row>
     <row r="116">
@@ -2139,16 +2139,16 @@
         <v>20.5</v>
       </c>
       <c r="B116" s="2">
-        <v>4.898817E-05</v>
+        <v>5.116918E-05</v>
       </c>
       <c r="C116" s="2">
-        <v>4.906483E-05</v>
+        <v>5.122852E-05</v>
       </c>
       <c r="D116" s="2">
-        <v>1.36809E-05</v>
+        <v>1.394429E-05</v>
       </c>
       <c r="E116" s="2">
-        <v>0.0001167107</v>
+        <v>0.0001112711</v>
       </c>
     </row>
     <row r="117">
@@ -2156,16 +2156,16 @@
         <v>20.75</v>
       </c>
       <c r="B117" s="2">
-        <v>4.889864E-05</v>
+        <v>5.107751E-05</v>
       </c>
       <c r="C117" s="2">
-        <v>4.897324E-05</v>
+        <v>5.113482E-05</v>
       </c>
       <c r="D117" s="2">
-        <v>1.376568E-05</v>
+        <v>1.403264E-05</v>
       </c>
       <c r="E117" s="2">
-        <v>0.0001164909</v>
+        <v>0.0001110657</v>
       </c>
     </row>
     <row r="118">
@@ -2173,16 +2173,16 @@
         <v>21</v>
       </c>
       <c r="B118" s="2">
-        <v>4.88106E-05</v>
+        <v>5.098748E-05</v>
       </c>
       <c r="C118" s="2">
-        <v>4.888318E-05</v>
+        <v>5.104279E-05</v>
       </c>
       <c r="D118" s="2">
-        <v>1.385025E-05</v>
+        <v>1.412077E-05</v>
       </c>
       <c r="E118" s="2">
-        <v>0.0001162747</v>
+        <v>0.0001108641</v>
       </c>
     </row>
     <row r="119">
@@ -2190,16 +2190,16 @@
         <v>21.25</v>
       </c>
       <c r="B119" s="2">
-        <v>4.8724E-05</v>
+        <v>5.089905E-05</v>
       </c>
       <c r="C119" s="2">
-        <v>4.879459E-05</v>
+        <v>5.095241E-05</v>
       </c>
       <c r="D119" s="2">
-        <v>1.393462E-05</v>
+        <v>1.420869E-05</v>
       </c>
       <c r="E119" s="2">
-        <v>0.0001160621</v>
+        <v>0.000110666</v>
       </c>
     </row>
     <row r="120">
@@ -2207,16 +2207,16 @@
         <v>21.5</v>
       </c>
       <c r="B120" s="2">
-        <v>4.863885E-05</v>
+        <v>5.08122E-05</v>
       </c>
       <c r="C120" s="2">
-        <v>4.87075E-05</v>
+        <v>5.086365E-05</v>
       </c>
       <c r="D120" s="2">
-        <v>1.40188E-05</v>
+        <v>1.42964E-05</v>
       </c>
       <c r="E120" s="2">
-        <v>0.0001158531</v>
+        <v>0.0001104715</v>
       </c>
     </row>
     <row r="121">
@@ -2224,16 +2224,16 @@
         <v>21.75</v>
       </c>
       <c r="B121" s="2">
-        <v>4.855511E-05</v>
+        <v>5.072688E-05</v>
       </c>
       <c r="C121" s="2">
-        <v>4.862186E-05</v>
+        <v>5.077647E-05</v>
       </c>
       <c r="D121" s="2">
-        <v>1.410279E-05</v>
+        <v>1.438392E-05</v>
       </c>
       <c r="E121" s="2">
-        <v>0.0001156475</v>
+        <v>0.0001102804</v>
       </c>
     </row>
     <row r="122">
@@ -2241,16 +2241,16 @@
         <v>22</v>
       </c>
       <c r="B122" s="2">
-        <v>4.847275E-05</v>
+        <v>5.064307E-05</v>
       </c>
       <c r="C122" s="2">
-        <v>4.853762E-05</v>
+        <v>5.069083E-05</v>
       </c>
       <c r="D122" s="2">
-        <v>1.418658E-05</v>
+        <v>1.447123E-05</v>
       </c>
       <c r="E122" s="2">
-        <v>0.0001154453</v>
+        <v>0.0001100928</v>
       </c>
     </row>
     <row r="123">
@@ -2258,16 +2258,16 @@
         <v>22.25</v>
       </c>
       <c r="B123" s="2">
-        <v>4.839173E-05</v>
+        <v>5.056074E-05</v>
       </c>
       <c r="C123" s="2">
-        <v>4.845477E-05</v>
+        <v>5.06067E-05</v>
       </c>
       <c r="D123" s="2">
-        <v>1.427019E-05</v>
+        <v>1.455835E-05</v>
       </c>
       <c r="E123" s="2">
-        <v>0.0001152465</v>
+        <v>0.0001099084</v>
       </c>
     </row>
     <row r="124">
@@ -2275,16 +2275,16 @@
         <v>22.5</v>
       </c>
       <c r="B124" s="2">
-        <v>4.831205E-05</v>
+        <v>5.047986E-05</v>
       </c>
       <c r="C124" s="2">
-        <v>4.837328E-05</v>
+        <v>5.052408E-05</v>
       </c>
       <c r="D124" s="2">
-        <v>1.435361E-05</v>
+        <v>1.464528E-05</v>
       </c>
       <c r="E124" s="2">
-        <v>0.000115051</v>
+        <v>0.0001097274</v>
       </c>
     </row>
     <row r="125">
@@ -2292,16 +2292,16 @@
         <v>22.75</v>
       </c>
       <c r="B125" s="2">
-        <v>4.823367E-05</v>
+        <v>5.040039E-05</v>
       </c>
       <c r="C125" s="2">
-        <v>4.829314E-05</v>
+        <v>5.04429E-05</v>
       </c>
       <c r="D125" s="2">
-        <v>1.443685E-05</v>
+        <v>1.473202E-05</v>
       </c>
       <c r="E125" s="2">
-        <v>0.0001148586</v>
+        <v>0.0001095495</v>
       </c>
     </row>
     <row r="126">
@@ -2309,16 +2309,16 @@
         <v>23</v>
       </c>
       <c r="B126" s="2">
-        <v>4.815659E-05</v>
+        <v>5.032232E-05</v>
       </c>
       <c r="C126" s="2">
-        <v>4.821433E-05</v>
+        <v>5.036316E-05</v>
       </c>
       <c r="D126" s="2">
-        <v>1.451991E-05</v>
+        <v>1.481856E-05</v>
       </c>
       <c r="E126" s="2">
-        <v>0.0001146695</v>
+        <v>0.0001093748</v>
       </c>
     </row>
     <row r="127">
@@ -2326,16 +2326,16 @@
         <v>23.25</v>
       </c>
       <c r="B127" s="2">
-        <v>4.808079E-05</v>
+        <v>5.024562E-05</v>
       </c>
       <c r="C127" s="2">
-        <v>4.813684E-05</v>
+        <v>5.028483E-05</v>
       </c>
       <c r="D127" s="2">
-        <v>1.460279E-05</v>
+        <v>1.490493E-05</v>
       </c>
       <c r="E127" s="2">
-        <v>0.0001144835</v>
+        <v>0.0001092031</v>
       </c>
     </row>
     <row r="128">
@@ -2343,16 +2343,16 @@
         <v>23.5</v>
       </c>
       <c r="B128" s="2">
-        <v>4.800623E-05</v>
+        <v>5.017025E-05</v>
       </c>
       <c r="C128" s="2">
-        <v>4.806061E-05</v>
+        <v>5.020787E-05</v>
       </c>
       <c r="D128" s="2">
-        <v>1.46855E-05</v>
+        <v>1.499111E-05</v>
       </c>
       <c r="E128" s="2">
-        <v>0.0001143006</v>
+        <v>0.0001090345</v>
       </c>
     </row>
     <row r="129">
@@ -2360,16 +2360,16 @@
         <v>23.75</v>
       </c>
       <c r="B129" s="2">
-        <v>4.793289E-05</v>
+        <v>5.009621E-05</v>
       </c>
       <c r="C129" s="2">
-        <v>4.798564E-05</v>
+        <v>5.013226E-05</v>
       </c>
       <c r="D129" s="2">
-        <v>1.476803E-05</v>
+        <v>1.507711E-05</v>
       </c>
       <c r="E129" s="2">
-        <v>0.0001141207</v>
+        <v>0.0001088688</v>
       </c>
     </row>
     <row r="130">
@@ -2377,16 +2377,16 @@
         <v>24</v>
       </c>
       <c r="B130" s="2">
-        <v>4.786077E-05</v>
+        <v>5.002345E-05</v>
       </c>
       <c r="C130" s="2">
-        <v>4.791192E-05</v>
+        <v>5.005798E-05</v>
       </c>
       <c r="D130" s="2">
-        <v>1.485039E-05</v>
+        <v>1.516293E-05</v>
       </c>
       <c r="E130" s="2">
-        <v>0.0001139438</v>
+        <v>0.0001087061</v>
       </c>
     </row>
   </sheetData>
@@ -2427,7 +2427,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="2">
-        <v>4697.93796539307</v>
+        <v>4413.52367401123</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>11</v>
@@ -2441,7 +2441,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="2">
-        <v>5077.15559005737</v>
+        <v>4740.54527282715</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>11</v>
@@ -2455,7 +2455,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="2">
-        <v>0.509677978698164</v>
+        <v>0.459297909401357</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>14</v>
@@ -2469,7 +2469,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="2">
-        <v>8283.37691602453</v>
+        <v>7538.91365989142</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>11</v>
@@ -2514,16 +2514,16 @@
         <v>20</v>
       </c>
       <c r="B2" s="2">
-        <v>0.583230912685394</v>
+        <v>0.624848902225494</v>
       </c>
       <c r="C2" s="2">
         <v>0</v>
       </c>
       <c r="D2" s="2">
-        <v>1.39222633838654</v>
+        <v>1.36073052883148</v>
       </c>
       <c r="E2" s="2">
-        <v>0.595903217792511</v>
+        <v>0.638074159622192</v>
       </c>
     </row>
     <row r="3">
@@ -2531,16 +2531,16 @@
         <v>21</v>
       </c>
       <c r="B3" s="2">
-        <v>1920299560546.88</v>
+        <v>2132108886718.75</v>
       </c>
       <c r="C3" s="2">
         <v>0</v>
       </c>
       <c r="D3" s="2">
-        <v>4583933105468.75</v>
+        <v>4643083496093.75</v>
       </c>
       <c r="E3" s="2">
-        <v>1962023193359.37</v>
+        <v>2177236083984.37</v>
       </c>
     </row>
     <row r="4">
@@ -2548,16 +2548,16 @@
         <v>22</v>
       </c>
       <c r="B4" s="2">
-        <v>0.115812823176384</v>
+        <v>0.118457205593586</v>
       </c>
       <c r="C4" s="2">
-        <v>0.0148074021562934</v>
+        <v>0.0150145534425974</v>
       </c>
       <c r="D4" s="2">
-        <v>0.290481269359589</v>
+        <v>0.270829826593399</v>
       </c>
       <c r="E4" s="2">
-        <v>0.119138307869434</v>
+        <v>0.121767811477184</v>
       </c>
     </row>
     <row r="5">
@@ -2565,16 +2565,16 @@
         <v>23</v>
       </c>
       <c r="B5" s="2">
-        <v>381316040039.063</v>
+        <v>404199584960.938</v>
       </c>
       <c r="C5" s="2">
-        <v>48753669738.7695</v>
+        <v>51232646942.1387</v>
       </c>
       <c r="D5" s="2">
-        <v>956415405273.438</v>
+        <v>924125244140.625</v>
       </c>
       <c r="E5" s="2">
-        <v>392265258789.063</v>
+        <v>415496002197.266</v>
       </c>
     </row>
     <row r="6">
@@ -2582,16 +2582,16 @@
         <v>24</v>
       </c>
       <c r="B6" s="2">
-        <v>0.00105374830309302</v>
+        <v>0.00104337208904326</v>
       </c>
       <c r="C6" s="2">
-        <v>1.48503913806053E-05</v>
+        <v>1.51629301399225E-05</v>
       </c>
       <c r="D6" s="2">
-        <v>0.0020713503472507</v>
+        <v>0.00197358475998044</v>
       </c>
       <c r="E6" s="2">
-        <v>0.00138942967168987</v>
+        <v>0.00136743672192097</v>
       </c>
     </row>
     <row r="7">
@@ -2599,16 +2599,16 @@
         <v>25</v>
       </c>
       <c r="B7" s="2">
-        <v>3469487.42866516</v>
+        <v>3560193.30024719</v>
       </c>
       <c r="C7" s="2">
-        <v>48895.2100276947</v>
+        <v>51738.9364540577</v>
       </c>
       <c r="D7" s="2">
-        <v>6819962.50152588</v>
+        <v>6734263.89694214</v>
       </c>
       <c r="E7" s="2">
-        <v>4574725.15106201</v>
+        <v>4665966.03393555</v>
       </c>
     </row>
     <row r="8">
@@ -2616,16 +2616,16 @@
         <v>26</v>
       </c>
       <c r="B8" s="2">
-        <v>4.79119189549237E-05</v>
+        <v>5.00579808431212E-05</v>
       </c>
       <c r="C8" s="2">
-        <v>1.48503913806053E-05</v>
+        <v>1.51629301399225E-05</v>
       </c>
       <c r="D8" s="2">
-        <v>0.000113943831820507</v>
+        <v>0.000108706059108954</v>
       </c>
       <c r="E8" s="2">
-        <v>4.7860768972896E-05</v>
+        <v>5.00234527862631E-05</v>
       </c>
     </row>
     <row r="9">
@@ -2633,16 +2633,16 @@
         <v>27</v>
       </c>
       <c r="B9" s="2">
-        <v>0.520752102602273</v>
+        <v>0.469019229058176</v>
       </c>
       <c r="C9" s="2" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="D9" s="2">
-        <v>0.218153276364319</v>
+        <v>0.215374122490175</v>
       </c>
       <c r="E9" s="2">
-        <v>0.509677978698164</v>
+        <v>0.459297909401357</v>
       </c>
     </row>
     <row r="10">
@@ -2650,16 +2650,16 @@
         <v>28</v>
       </c>
       <c r="B10" s="2">
-        <v>0.801428854465485</v>
+        <v>0.810422658920288</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D10" s="2">
-        <v>0.791354835033417</v>
+        <v>0.800967335700989</v>
       </c>
       <c r="E10" s="2">
-        <v>0.800071060657501</v>
+        <v>0.809163570404053</v>
       </c>
     </row>
     <row r="11">
@@ -2667,16 +2667,16 @@
         <v>30</v>
       </c>
       <c r="B11" s="2">
-        <v>151.16416015625</v>
+        <v>157.658235677083</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D11" s="2">
-        <v>148.148111979167</v>
+        <v>154.641764322917</v>
       </c>
       <c r="E11" s="2">
-        <v>153.624381510417</v>
+        <v>160.154720052083</v>
       </c>
     </row>
     <row r="12">
@@ -2701,16 +2701,16 @@
         <v>32</v>
       </c>
       <c r="B13" s="2">
-        <v>112.703181966146</v>
+        <v>116.865804036458</v>
       </c>
       <c r="C13" s="2">
-        <v>-31.1583231608073</v>
+        <v>-30.5288269042969</v>
       </c>
       <c r="D13" s="2">
-        <v>111.702913411458</v>
+        <v>115.826359049479</v>
       </c>
       <c r="E13" s="2">
-        <v>115.079720052083</v>
+        <v>119.236173502604</v>
       </c>
     </row>
     <row r="14">
@@ -2718,16 +2718,16 @@
         <v>33</v>
       </c>
       <c r="B14" s="2">
-        <v>5080.3427696228</v>
+        <v>4744.64654922485</v>
       </c>
       <c r="C14" s="2" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="D14" s="2">
-        <v>2109.36641693115</v>
+        <v>2159.36827659607</v>
       </c>
       <c r="E14" s="2">
-        <v>5077.15559005737</v>
+        <v>4740.54527282715</v>
       </c>
     </row>
     <row r="15">
@@ -2735,16 +2735,16 @@
         <v>34</v>
       </c>
       <c r="B15" s="2">
-        <v>4723.14357757568</v>
+        <v>4436.68460845947</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D15" s="2">
-        <v>1939.13984298706</v>
+        <v>1998.34990501404</v>
       </c>
       <c r="E15" s="2">
-        <v>4697.93796539307</v>
+        <v>4413.52367401123</v>
       </c>
     </row>
   </sheetData>
